--- a/BDD.xlsx
+++ b/BDD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\charl\solar-data-china\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E767DF-1232-4D74-A522-C4C179B0A226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8D78C5-AECA-488B-90B8-65D13D2CD123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="9960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>

--- a/BDD.xlsx
+++ b/BDD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\charl\solar-data-china\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8D78C5-AECA-488B-90B8-65D13D2CD123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA849772-E891-4DA7-B142-CB21D999BE63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="233">
   <si>
     <t>Name</t>
   </si>
@@ -722,9 +722,6 @@
     <t>https://www.sciencedirect.com/science/article/pii/S0360544217309891?via%3Dihub</t>
   </si>
   <si>
-    <t>Texture is important in improving the accuracy of mapping Photovoltaic power plants : a case study of Ningxiq Autonomous Region, China</t>
-  </si>
-  <si>
     <t>Harmonised global datasets of wind and solar farm locations and power</t>
   </si>
   <si>
@@ -826,12 +823,6 @@
 overall accuracy over 96% for both 2015 (OA = 96.71%) and 2020 (OA = 99.06%) =&gt; because RF classifier was trained on 2020
 Consistency evaluation and accuracy comparison with existing PV dataset 
 </t>
-  </si>
-  <si>
-    <t>https://www.rystadenergy.com/news/china-rooftop-solar-installations-hit-record-in-1q25</t>
-  </si>
-  <si>
-    <t>https://www.pv-magazine.com/2025/06/23/china-hits-1-tw-solar-milestone/</t>
   </si>
   <si>
     <t>https://arxiv.org/abs/2202.01340</t>
@@ -1075,6 +1066,91 @@
   </si>
   <si>
     <t xml:space="preserve">Global Renewables Watch: A Temporal Dataset of Solar and Wind Energy Derived from Satellite </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yuehong Chen and al. </t>
+  </si>
+  <si>
+    <t>Remote Senseing of Environment, Volume 305</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0034425724001111</t>
+  </si>
+  <si>
+    <t>global inventory of commercial-, industrial- and utility-scale PV installations (PV generating stations in excess of 10 kilowatts nameplate capacity) by using a longitudinal corpus of remote sensing imagery, machine learning and a large cloud computation infrastructure. Located and verified 68,661 facilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landasat 8 imagery ,
+U-Net to map China </t>
+  </si>
+  <si>
+    <t>https://chinaenergyportal.org/en/2020-q2-pv-installations-utility-and-distributed-by-province</t>
+  </si>
+  <si>
+    <t>2020 Q2 PV installations utility and distributed by province</t>
+  </si>
+  <si>
+    <t>https://www.nea.gov.cn/20250221/f04452701c914d51a89d0c0ea6f4acd1/c.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024 PV installations utility and distributed by province </t>
+  </si>
+  <si>
+    <t>https://www.nea.gov.cn/20250811/b32802d80ef04148b704e6bc1cd51eb2/c.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 PV S1 intallations utility and distributed by province </t>
+  </si>
+  <si>
+    <t>https://www.nea.gov.cn/2023-07/27/c_1310734298.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023 PV S1 intallations utility and distributed by province </t>
+  </si>
+  <si>
+    <t>https://www.nea.gov.cn/2023-02/17/c_1310698128.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 PV installations utility and distributed by province </t>
+  </si>
+  <si>
+    <t>https://www.nea.gov.cn/2022-03/09/c_1310508114.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021 PV installations utility and distributed by province </t>
+  </si>
+  <si>
+    <t>Household PV project information (December 2021)</t>
+  </si>
+  <si>
+    <t>https://chinaenergyportal.org/household-pv-project-information-december-2021/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpenStreet Map </t>
+  </si>
+  <si>
+    <t>The study used OpenStreetMap (OSM) data to identify wind and solar installations worldwide. Researchers analyzed OSM’s tagging system, selecting the most reliable key/value pairs to extract information on power plants, generators, and their energy sources. From this, they built the first open, harmonized global dataset of solar PV and wind farms, available in vector formats (geopackages, shapefiles, CSV). The dataset includes both grouped farms and single installations, with metadata on urban or water-related locations and estimated power capacity.</t>
+  </si>
+  <si>
+    <t>This study develops a framework using Sentinel-2 (2015-today) and Landsat imagery to extract both the spatial extent and installation dates of PV plants, construct a comprehensive geospatial dataset from 2010 to 2022</t>
+  </si>
+  <si>
+    <t>TransUNet</t>
+  </si>
+  <si>
+    <t>Quanlong Feng and al.</t>
+  </si>
+  <si>
+    <t>Scientific Data, 11, 198</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41597-024-02994-x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This study presents the first publicly available 10-meter national map of ground-mounted photovoltaic power stations in China for 2020. Using Sentinel-2 imagery, a Random Forest classifier and Google Earth Engine, the authors mapped PV stations with high accuracy, employing provincial partitioning and active learning to address data imbalance. </t>
+  </si>
+  <si>
+    <t>Sentinel 2, RF, provincial partitioning</t>
   </si>
 </sst>
 </file>
@@ -1259,6 +1335,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1283,7 +1360,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1429,15 +1506,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2255,7 +2333,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="39.6">
+    <row r="3" spans="1:15" ht="26.4">
       <c r="A3" s="5" t="s">
         <v>20</v>
       </c>
@@ -2368,7 +2446,7 @@
       </c>
       <c r="O5" s="18"/>
     </row>
-    <row r="6" spans="1:15" ht="198">
+    <row r="6" spans="1:15" ht="184.8">
       <c r="A6" s="2" t="s">
         <v>35</v>
       </c>
@@ -3039,7 +3117,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L1003"/>
+  <dimension ref="A1:L1002"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="36.77734375" style="31" customWidth="1"/>
@@ -3124,7 +3202,7 @@
         <v>83</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C3" s="13">
         <v>2024</v>
@@ -3136,19 +3214,19 @@
         <v>85</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H3" s="30" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>86</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="140.4" customHeight="1">
@@ -3171,22 +3249,22 @@
         <v>129</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="12" t="s">
         <v>128</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="409.2" customHeight="1">
       <c r="A5" s="50" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C5" s="40" t="s">
         <v>115</v>
@@ -3196,27 +3274,27 @@
         <v>116</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="H5" s="54" t="s">
-        <v>190</v>
-      </c>
-      <c r="I5" s="54" t="s">
+        <v>188</v>
+      </c>
+      <c r="H5" s="53" t="s">
+        <v>187</v>
+      </c>
+      <c r="I5" s="53" t="s">
+        <v>186</v>
+      </c>
+      <c r="J5" s="18" t="s">
         <v>189</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="409.2" customHeight="1">
       <c r="A6" s="50" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C6" s="42">
         <v>2022</v>
@@ -3225,20 +3303,20 @@
         <v>88</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I6" s="41"/>
       <c r="J6" s="18" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="52.8">
@@ -3257,7 +3335,12 @@
       <c r="E7" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="G7" s="11"/>
+      <c r="F7" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>209</v>
+      </c>
       <c r="H7" s="17"/>
       <c r="I7" s="41"/>
       <c r="J7" s="11"/>
@@ -3267,22 +3350,22 @@
         <v>130</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C8" s="42">
         <v>2018</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>144</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H8" s="39" t="s">
         <v>145</v>
@@ -3291,7 +3374,7 @@
         <v>2017</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="409.2" customHeight="1">
@@ -3299,55 +3382,60 @@
         <v>147</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="C9" s="55">
+        <v>198</v>
+      </c>
+      <c r="C9" s="54">
         <v>2022</v>
       </c>
       <c r="D9" s="42" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E9" s="39" t="s">
         <v>146</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H9" s="39" t="s">
         <v>131</v>
       </c>
       <c r="I9" s="18" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="52.8">
       <c r="A10" s="48" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C10" s="40">
         <v>2020</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="G10" s="11"/>
+        <v>155</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>224</v>
+      </c>
       <c r="H10" s="39" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I10" s="41"/>
       <c r="J10" s="11"/>
     </row>
-    <row r="11" spans="1:12" ht="26.4">
+    <row r="11" spans="1:12" ht="26.4" hidden="1">
       <c r="A11" s="29" t="s">
         <v>133</v>
       </c>
@@ -3362,7 +3450,7 @@
       <c r="I11" s="41"/>
       <c r="J11" s="11"/>
     </row>
-    <row r="12" spans="1:12" ht="66">
+    <row r="12" spans="1:12" ht="66" hidden="1">
       <c r="A12" s="29" t="s">
         <v>134</v>
       </c>
@@ -3377,7 +3465,7 @@
       <c r="I12" s="41"/>
       <c r="J12" s="11"/>
     </row>
-    <row r="13" spans="1:12" ht="39.6">
+    <row r="13" spans="1:12" ht="39.6" hidden="1">
       <c r="A13" s="48" t="s">
         <v>136</v>
       </c>
@@ -3392,7 +3480,7 @@
       <c r="I13" s="41"/>
       <c r="J13" s="11"/>
     </row>
-    <row r="14" spans="1:12" ht="66">
+    <row r="14" spans="1:12" ht="66" hidden="1">
       <c r="A14" s="48" t="s">
         <v>138</v>
       </c>
@@ -3407,7 +3495,7 @@
       <c r="I14" s="41"/>
       <c r="J14" s="11"/>
     </row>
-    <row r="15" spans="1:12" ht="39.6">
+    <row r="15" spans="1:12" ht="39.6" hidden="1">
       <c r="A15" s="48" t="s">
         <v>140</v>
       </c>
@@ -3422,7 +3510,7 @@
       <c r="I15" s="41"/>
       <c r="J15" s="11"/>
     </row>
-    <row r="16" spans="1:12" ht="39.6">
+    <row r="16" spans="1:12" ht="39.6" hidden="1">
       <c r="A16" s="48" t="s">
         <v>142</v>
       </c>
@@ -3437,7 +3525,7 @@
       <c r="I16" s="41"/>
       <c r="J16" s="11"/>
     </row>
-    <row r="17" spans="1:10" ht="39.6">
+    <row r="17" spans="1:10" ht="39.6" hidden="1">
       <c r="A17" s="48" t="s">
         <v>148</v>
       </c>
@@ -3452,7 +3540,7 @@
       <c r="I17" s="41"/>
       <c r="J17" s="11"/>
     </row>
-    <row r="18" spans="1:10" ht="26.4">
+    <row r="18" spans="1:10" ht="26.4" hidden="1">
       <c r="A18" s="29" t="s">
         <v>150</v>
       </c>
@@ -3467,7 +3555,7 @@
       <c r="I18" s="41"/>
       <c r="J18" s="11"/>
     </row>
-    <row r="19" spans="1:10" ht="39.6">
+    <row r="19" spans="1:10" ht="39.6" hidden="1">
       <c r="A19" s="49" t="s">
         <v>152</v>
       </c>
@@ -3483,39 +3571,37 @@
       <c r="I19" s="41"/>
       <c r="J19" s="11"/>
     </row>
-    <row r="20" spans="1:10" ht="55.2" customHeight="1">
-      <c r="A20" s="49" t="s">
-        <v>154</v>
+    <row r="20" spans="1:10" ht="55.2" hidden="1" customHeight="1">
+      <c r="A20" s="48" t="s">
+        <v>156</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="42"/>
       <c r="D20" s="1"/>
       <c r="E20" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="F20" s="53"/>
+        <v>157</v>
+      </c>
+      <c r="F20" s="52"/>
       <c r="G20" s="11"/>
       <c r="H20" s="17"/>
       <c r="I20" s="41"/>
       <c r="J20" s="11"/>
     </row>
-    <row r="21" spans="1:10" ht="55.2" customHeight="1">
-      <c r="A21" s="48" t="s">
-        <v>157</v>
+    <row r="21" spans="1:10" ht="52.8" hidden="1">
+      <c r="A21" s="49" t="s">
+        <v>158</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="42"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="16" t="s">
-        <v>158</v>
-      </c>
+      <c r="E21" s="47"/>
       <c r="F21" s="52"/>
       <c r="G21" s="11"/>
       <c r="H21" s="17"/>
       <c r="I21" s="41"/>
       <c r="J21" s="11"/>
     </row>
-    <row r="22" spans="1:10" ht="52.8">
+    <row r="22" spans="1:10" ht="39.6" hidden="1">
       <c r="A22" s="49" t="s">
         <v>159</v>
       </c>
@@ -3523,13 +3609,13 @@
       <c r="C22" s="42"/>
       <c r="D22" s="1"/>
       <c r="E22" s="47"/>
-      <c r="F22" s="52"/>
+      <c r="F22" s="11"/>
       <c r="G22" s="11"/>
       <c r="H22" s="17"/>
       <c r="I22" s="41"/>
       <c r="J22" s="11"/>
     </row>
-    <row r="23" spans="1:10" ht="39.6">
+    <row r="23" spans="1:10" ht="66" hidden="1">
       <c r="A23" s="49" t="s">
         <v>160</v>
       </c>
@@ -3543,37 +3629,37 @@
       <c r="I23" s="41"/>
       <c r="J23" s="11"/>
     </row>
-    <row r="24" spans="1:10" ht="66">
-      <c r="A24" s="49" t="s">
+    <row r="24" spans="1:10" ht="39.6" hidden="1">
+      <c r="A24" s="48" t="s">
         <v>161</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="42"/>
       <c r="D24" s="1"/>
-      <c r="E24" s="47"/>
+      <c r="E24" s="16" t="s">
+        <v>162</v>
+      </c>
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
       <c r="H24" s="17"/>
       <c r="I24" s="41"/>
       <c r="J24" s="11"/>
     </row>
-    <row r="25" spans="1:10" ht="39.6">
-      <c r="A25" s="48" t="s">
-        <v>162</v>
+    <row r="25" spans="1:10" ht="39.6" hidden="1">
+      <c r="A25" s="29" t="s">
+        <v>166</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="42"/>
       <c r="D25" s="1"/>
-      <c r="E25" s="16" t="s">
-        <v>163</v>
-      </c>
+      <c r="E25" s="47"/>
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
       <c r="H25" s="17"/>
       <c r="I25" s="41"/>
       <c r="J25" s="11"/>
     </row>
-    <row r="26" spans="1:10" ht="39.6">
+    <row r="26" spans="1:10" ht="52.8" hidden="1">
       <c r="A26" s="29" t="s">
         <v>167</v>
       </c>
@@ -3587,12 +3673,14 @@
       <c r="I26" s="41"/>
       <c r="J26" s="11"/>
     </row>
-    <row r="27" spans="1:10" ht="52.8">
+    <row r="27" spans="1:10" ht="66" hidden="1">
       <c r="A27" s="29" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B27" s="3"/>
-      <c r="C27" s="42"/>
+      <c r="C27" s="42">
+        <v>2023</v>
+      </c>
       <c r="D27" s="1"/>
       <c r="E27" s="47"/>
       <c r="F27" s="11"/>
@@ -3601,14 +3689,12 @@
       <c r="I27" s="41"/>
       <c r="J27" s="11"/>
     </row>
-    <row r="28" spans="1:10" ht="66">
+    <row r="28" spans="1:10" ht="39.6" hidden="1">
       <c r="A28" s="29" t="s">
         <v>172</v>
       </c>
       <c r="B28" s="3"/>
-      <c r="C28" s="42">
-        <v>2023</v>
-      </c>
+      <c r="C28" s="42"/>
       <c r="D28" s="1"/>
       <c r="E28" s="47"/>
       <c r="F28" s="11"/>
@@ -3617,21 +3703,33 @@
       <c r="I28" s="41"/>
       <c r="J28" s="11"/>
     </row>
-    <row r="29" spans="1:10" ht="39.6">
+    <row r="29" spans="1:10" ht="52.8">
       <c r="A29" s="29" t="s">
         <v>173</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="42"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
+      <c r="B29" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C29" s="42">
+        <v>2024</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E29" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="G29" s="47" t="s">
+        <v>227</v>
+      </c>
       <c r="H29" s="17"/>
       <c r="I29" s="41"/>
       <c r="J29" s="11"/>
     </row>
-    <row r="30" spans="1:10" ht="52.8">
+    <row r="30" spans="1:10" ht="39.6" hidden="1">
       <c r="A30" s="29" t="s">
         <v>174</v>
       </c>
@@ -3645,9 +3743,9 @@
       <c r="I30" s="41"/>
       <c r="J30" s="11"/>
     </row>
-    <row r="31" spans="1:10" ht="39.6">
+    <row r="31" spans="1:10" ht="39.6" hidden="1">
       <c r="A31" s="29" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="42"/>
@@ -3659,9 +3757,9 @@
       <c r="I31" s="41"/>
       <c r="J31" s="11"/>
     </row>
-    <row r="32" spans="1:10" ht="39.6">
+    <row r="32" spans="1:10" ht="39.6" hidden="1">
       <c r="A32" s="29" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="42"/>
@@ -3675,14 +3773,26 @@
     </row>
     <row r="33" spans="1:10" ht="39.6">
       <c r="A33" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="42"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
+        <v>174</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C33" s="42">
+        <v>2024</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>232</v>
+      </c>
       <c r="H33" s="17"/>
       <c r="I33" s="41"/>
       <c r="J33" s="11"/>
@@ -8527,15 +8637,10 @@
       <c r="B1001" s="1"/>
       <c r="D1001" s="1"/>
     </row>
-    <row r="1002" spans="1:4" ht="13.2">
+    <row r="1002" spans="1:4" ht="15.75" customHeight="1">
       <c r="A1002" s="3"/>
       <c r="B1002" s="1"/>
       <c r="D1002" s="1"/>
-    </row>
-    <row r="1003" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A1003" s="3"/>
-      <c r="B1003" s="1"/>
-      <c r="D1003" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -8556,43 +8661,99 @@
     <hyperlink ref="E17" r:id="rId15" xr:uid="{55A59522-8FBD-4A43-B576-D4CE614341D7}"/>
     <hyperlink ref="E18" r:id="rId16" xr:uid="{5B989690-003F-4923-B7F4-A47A85945677}"/>
     <hyperlink ref="E19" r:id="rId17" xr:uid="{1F44A843-12CF-4E9B-A153-243927E180AA}"/>
-    <hyperlink ref="E20" r:id="rId18" xr:uid="{E206D339-90EF-431C-A40C-1EA010BA239D}"/>
-    <hyperlink ref="E10" r:id="rId19" xr:uid="{F9100E57-6F7E-4BBD-91B2-826029FEB248}"/>
-    <hyperlink ref="E21" r:id="rId20" xr:uid="{766864F1-8314-4690-BDD1-403D573EE1A2}"/>
-    <hyperlink ref="E25" r:id="rId21" xr:uid="{7243A186-84D9-4A2B-A3C9-2D8B161DBD81}"/>
-    <hyperlink ref="H8" r:id="rId22" xr:uid="{5AF6AD83-A0DB-402A-9E62-981A344C4043}"/>
-    <hyperlink ref="H3" r:id="rId23" display="https://zenodo.org/records/14292571" xr:uid="{B8E688FD-5EF4-4175-B267-588646FB1807}"/>
-    <hyperlink ref="E6" r:id="rId24" xr:uid="{3AC147B4-BB92-4910-8D62-00FDAADC05B1}"/>
-    <hyperlink ref="H10" r:id="rId25" xr:uid="{8E9BCBE4-EEA1-4B02-B7E5-3B46AEA87B92}"/>
-    <hyperlink ref="H6" r:id="rId26" xr:uid="{8F125A05-13A9-4DD6-ABFD-E7C8A8884495}"/>
-    <hyperlink ref="H9" r:id="rId27" xr:uid="{012E501A-B24C-4F88-B6C0-9023134D2BE7}"/>
+    <hyperlink ref="E10" r:id="rId18" xr:uid="{F9100E57-6F7E-4BBD-91B2-826029FEB248}"/>
+    <hyperlink ref="E20" r:id="rId19" xr:uid="{766864F1-8314-4690-BDD1-403D573EE1A2}"/>
+    <hyperlink ref="E24" r:id="rId20" xr:uid="{7243A186-84D9-4A2B-A3C9-2D8B161DBD81}"/>
+    <hyperlink ref="H8" r:id="rId21" xr:uid="{5AF6AD83-A0DB-402A-9E62-981A344C4043}"/>
+    <hyperlink ref="H3" r:id="rId22" display="https://zenodo.org/records/14292571" xr:uid="{B8E688FD-5EF4-4175-B267-588646FB1807}"/>
+    <hyperlink ref="E6" r:id="rId23" xr:uid="{3AC147B4-BB92-4910-8D62-00FDAADC05B1}"/>
+    <hyperlink ref="H10" r:id="rId24" xr:uid="{8E9BCBE4-EEA1-4B02-B7E5-3B46AEA87B92}"/>
+    <hyperlink ref="H6" r:id="rId25" xr:uid="{8F125A05-13A9-4DD6-ABFD-E7C8A8884495}"/>
+    <hyperlink ref="H9" r:id="rId26" xr:uid="{012E501A-B24C-4F88-B6C0-9023134D2BE7}"/>
+    <hyperlink ref="E29" r:id="rId27" xr:uid="{264A10A7-ED74-4592-A835-B77FAC1AA493}"/>
+    <hyperlink ref="E33" r:id="rId28" xr:uid="{1A5407BE-52B6-4A9D-8C02-6C9B2861D2A2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId28"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId29"/>
   <tableParts count="1">
-    <tablePart r:id="rId29"/>
+    <tablePart r:id="rId30"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94EFB111-2AE6-4D75-8E3A-E95B2EFD8BE2}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <cols>
+    <col min="1" max="1" width="52.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="51" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>178</v>
+    <row r="1" spans="1:2">
+      <c r="A1" s="55" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1" s="51" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="56" t="s">
+        <v>221</v>
+      </c>
+      <c r="B2" s="51" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="56" t="s">
+        <v>219</v>
+      </c>
+      <c r="B3" s="51" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="56" t="s">
+        <v>217</v>
+      </c>
+      <c r="B4" s="51" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="56" t="s">
+        <v>213</v>
+      </c>
+      <c r="B5" s="51" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="56" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="51" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="55" t="s">
+        <v>222</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>223</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" xr:uid="{78BCC3A4-1946-464F-90D2-D6D75E4D10CE}"/>
+    <hyperlink ref="B1" r:id="rId1" xr:uid="{86E8418D-57F3-4C25-9CBA-E3127B633F65}"/>
+    <hyperlink ref="B5" r:id="rId2" xr:uid="{0A2B2D9F-1280-4220-BC52-D90253287502}"/>
+    <hyperlink ref="B6" r:id="rId3" xr:uid="{B83152B8-C9E3-4844-95C8-58359E756BDB}"/>
+    <hyperlink ref="B4" r:id="rId4" xr:uid="{17168A88-40FC-4DEF-819D-9E7C95E700C4}"/>
+    <hyperlink ref="B3" r:id="rId5" xr:uid="{539539E0-9848-412E-A96E-B1EFC33CEED4}"/>
+    <hyperlink ref="B2" r:id="rId6" xr:uid="{2261B650-FBA6-49A3-B534-0335A5236800}"/>
+    <hyperlink ref="B8" r:id="rId7" xr:uid="{F99EC302-B61C-4879-B479-E331D3C83887}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/BDD.xlsx
+++ b/BDD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\charl\solar-data-china\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA849772-E891-4DA7-B142-CB21D999BE63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84299A39-628C-4643-8691-379943766827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1164" windowWidth="17280" windowHeight="9960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
@@ -2333,7 +2333,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="26.4">
+    <row r="3" spans="1:15" ht="39.6">
       <c r="A3" s="5" t="s">
         <v>20</v>
       </c>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O5" s="18"/>
     </row>
-    <row r="6" spans="1:15" ht="184.8">
+    <row r="6" spans="1:15" ht="198">
       <c r="A6" s="2" t="s">
         <v>35</v>
       </c>
